--- a/artfynd/A 28151-2025 artfynd.xlsx
+++ b/artfynd/A 28151-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133622580</v>
       </c>
       <c r="B2" t="n">
-        <v>58393</v>
+        <v>58400</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>133622542</v>
       </c>
       <c r="B3" t="n">
-        <v>58090</v>
+        <v>58097</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28151-2025 artfynd.xlsx
+++ b/artfynd/A 28151-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133622580</v>
       </c>
       <c r="B2" t="n">
-        <v>58400</v>
+        <v>58410</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>133622542</v>
       </c>
       <c r="B3" t="n">
-        <v>58097</v>
+        <v>58107</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28151-2025 artfynd.xlsx
+++ b/artfynd/A 28151-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133622580</v>
+        <v>133622523</v>
       </c>
       <c r="B2" t="n">
-        <v>58410</v>
+        <v>57969</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103001</v>
+        <v>102977</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -718,17 +718,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hästhagen, Vg</t>
+          <t>Råstorp, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>382719</v>
+        <v>382854</v>
       </c>
       <c r="R2" t="n">
-        <v>6413469</v>
+        <v>6413466</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133622542</v>
+        <v>133622580</v>
       </c>
       <c r="B3" t="n">
-        <v>58107</v>
+        <v>58410</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,21 +805,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205976</v>
+        <v>103001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -831,23 +831,23 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Råstorpshage, Vg</t>
+          <t>Hästhagen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>382699</v>
+        <v>382719</v>
       </c>
       <c r="R3" t="n">
-        <v>6413450</v>
+        <v>6413469</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -910,6 +910,125 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133622542</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58107</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Råstorpshage, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>382699</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6413450</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fristad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>04:20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Eskil Friberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Eskil Friberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
